--- a/Raw/260218_UWS.xlsx
+++ b/Raw/260218_UWS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katia\Desktop\STAGE\M1\Travail\Stage_M1_UWS\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B385280B-FE0F-477F-BB76-E14086FA3BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95AFA04-44C2-4995-BC96-A0D437D3CB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="5" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
   </bookViews>
   <sheets>
     <sheet name="UWS" sheetId="2" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Neuilly" sheetId="6" r:id="rId3"/>
     <sheet name="7e" sheetId="5" r:id="rId4"/>
     <sheet name="19e" sheetId="4" r:id="rId5"/>
-    <sheet name="TEST" sheetId="3" r:id="rId6"/>
-    <sheet name="Vegetalisation" sheetId="1" r:id="rId7"/>
+    <sheet name="5e" sheetId="8" r:id="rId6"/>
+    <sheet name="TEST" sheetId="3" r:id="rId7"/>
+    <sheet name="Vegetalisation" sheetId="1" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -350,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="249">
   <si>
     <r>
       <t>Structural complexity</t>
@@ -1517,12 +1518,126 @@
   <si>
     <t>IN METERS</t>
   </si>
+  <si>
+    <t>May 2025</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vegetalised roof, trees and spontaneous small plants, so estimating the planting intervention was quite complicated. We're not considering trees, but the roof was defenety planted, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>but</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> there's also wild spontaneous flowers and seedlings, so I still put 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>Grids around the tree base in almost every tree, overgrown (cant see on photo)</t>
+  </si>
+  <si>
+    <t>April 2021</t>
+  </si>
+  <si>
+    <t>July 2020</t>
+  </si>
+  <si>
+    <t>Small pavemeny as irregular topography, with large spaces between one another</t>
+  </si>
+  <si>
+    <t>October 2022</t>
+  </si>
+  <si>
+    <t>The plants themselves are not obviously planted, but the context make them obviusly planted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odd </t>
+  </si>
+  <si>
+    <t>Same for the planted vegetation</t>
+  </si>
+  <si>
+    <t>5e</t>
+  </si>
+  <si>
+    <t>48.85243, 2.3461</t>
+  </si>
+  <si>
+    <t>48.84765, 2.34103</t>
+  </si>
+  <si>
+    <t>48.84036, 2.35055</t>
+  </si>
+  <si>
+    <t>48.83832, 2.34562</t>
+  </si>
+  <si>
+    <t>48.84553, 2.34582</t>
+  </si>
+  <si>
+    <t>48.83786, 2.35531</t>
+  </si>
+  <si>
+    <t>48.83866, 2.35782</t>
+  </si>
+  <si>
+    <t>48.84201, 2.34782</t>
+  </si>
+  <si>
+    <t>48.8406, 2.34081</t>
+  </si>
+  <si>
+    <t>48.84979, 2.34862</t>
+  </si>
+  <si>
+    <t>48.84241, 2.34977</t>
+  </si>
+  <si>
+    <t>48.84289, 2.36398</t>
+  </si>
+  <si>
+    <t>48.83806, 2.34395</t>
+  </si>
+  <si>
+    <t>48.84954, 2.35209</t>
+  </si>
+  <si>
+    <t>48.84782, 2.35143</t>
+  </si>
+  <si>
+    <t>48.84457, 2.34721</t>
+  </si>
+  <si>
+    <t>48.84226, 2.34131</t>
+  </si>
+  <si>
+    <t>48.83864, 2.35059</t>
+  </si>
+  <si>
+    <t>48.84657, 2.34899</t>
+  </si>
+  <si>
+    <t>48.8484, 2.35024</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1673,8 +1788,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1727,6 +1870,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1786,7 +1935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1942,6 +2091,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2442,28 +2615,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="71.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
+      <c r="D1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
       <c r="T1" s="20"/>
       <c r="U1" s="20"/>
     </row>
@@ -3302,28 +3475,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
+      <c r="J1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
     </row>
@@ -5719,28 +5892,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
+      <c r="J1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
     </row>
@@ -8237,28 +8410,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
+      <c r="J1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
     </row>
@@ -11381,28 +11554,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="71.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
+      <c r="J1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
     </row>
@@ -15372,6 +15545,2113 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7DD28B-8EFA-4DA7-B21C-491A7BA86BBF}">
+  <dimension ref="A1:AI22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="71.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="J1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+    </row>
+    <row r="2" spans="1:35" s="10" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH2" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="56">
+        <v>1</v>
+      </c>
+      <c r="D3" s="56">
+        <v>0</v>
+      </c>
+      <c r="E3" s="56">
+        <v>0</v>
+      </c>
+      <c r="F3" s="56">
+        <v>0</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="I3" s="58">
+        <v>0</v>
+      </c>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="58"/>
+      <c r="V3" s="58"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="58"/>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A4" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="53">
+        <v>2</v>
+      </c>
+      <c r="D4" s="53">
+        <v>1</v>
+      </c>
+      <c r="E4" s="53">
+        <v>0</v>
+      </c>
+      <c r="F4" s="53">
+        <v>2</v>
+      </c>
+      <c r="G4" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="55">
+        <v>3</v>
+      </c>
+      <c r="J4" s="55">
+        <v>1</v>
+      </c>
+      <c r="K4" s="55">
+        <v>1</v>
+      </c>
+      <c r="L4" s="55">
+        <v>0</v>
+      </c>
+      <c r="M4" s="55">
+        <v>0</v>
+      </c>
+      <c r="N4" s="55">
+        <v>1</v>
+      </c>
+      <c r="O4" s="55">
+        <v>1</v>
+      </c>
+      <c r="P4" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="55">
+        <v>0</v>
+      </c>
+      <c r="R4" s="55">
+        <v>1</v>
+      </c>
+      <c r="S4" s="55">
+        <v>0</v>
+      </c>
+      <c r="T4" s="55">
+        <v>0</v>
+      </c>
+      <c r="U4" s="55">
+        <v>1</v>
+      </c>
+      <c r="V4" s="55">
+        <v>1</v>
+      </c>
+      <c r="W4" s="55">
+        <v>0</v>
+      </c>
+      <c r="X4" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="55">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="55">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="55">
+        <v>8</v>
+      </c>
+      <c r="AD4" s="55">
+        <v>3.3333333330000001</v>
+      </c>
+      <c r="AE4" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="55">
+        <v>3</v>
+      </c>
+      <c r="AG4" s="55">
+        <v>2.4444444440000002</v>
+      </c>
+      <c r="AH4" s="60" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="53">
+        <v>3</v>
+      </c>
+      <c r="D5" s="53">
+        <v>1</v>
+      </c>
+      <c r="E5" s="53">
+        <v>0</v>
+      </c>
+      <c r="F5" s="53">
+        <v>2</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="55">
+        <v>3</v>
+      </c>
+      <c r="J5" s="55">
+        <v>1</v>
+      </c>
+      <c r="K5" s="55">
+        <v>1</v>
+      </c>
+      <c r="L5" s="55">
+        <v>1</v>
+      </c>
+      <c r="M5" s="55">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="55">
+        <v>1</v>
+      </c>
+      <c r="P5" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="55">
+        <v>1</v>
+      </c>
+      <c r="S5" s="55">
+        <v>0</v>
+      </c>
+      <c r="T5" s="55">
+        <v>0</v>
+      </c>
+      <c r="U5" s="55">
+        <v>0</v>
+      </c>
+      <c r="V5" s="55">
+        <v>1</v>
+      </c>
+      <c r="W5" s="2">
+        <v>1</v>
+      </c>
+      <c r="X5" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="55">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="55">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="55">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="55">
+        <v>4.1666666670000003</v>
+      </c>
+      <c r="AE5" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="55">
+        <v>4</v>
+      </c>
+      <c r="AG5" s="55">
+        <v>3.0555555559999998</v>
+      </c>
+      <c r="AH5" s="55" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A6" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="56">
+        <v>4</v>
+      </c>
+      <c r="D6" s="56">
+        <v>0</v>
+      </c>
+      <c r="E6" s="56">
+        <v>0</v>
+      </c>
+      <c r="F6" s="56">
+        <v>0</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="58">
+        <v>0</v>
+      </c>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
+      <c r="V6" s="58"/>
+      <c r="W6" s="59"/>
+      <c r="X6" s="59"/>
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="58"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A7" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="53">
+        <v>5</v>
+      </c>
+      <c r="D7" s="53">
+        <v>0</v>
+      </c>
+      <c r="E7" s="53">
+        <v>0</v>
+      </c>
+      <c r="F7" s="53">
+        <v>1</v>
+      </c>
+      <c r="G7" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" s="55">
+        <v>1</v>
+      </c>
+      <c r="J7" s="55">
+        <v>1</v>
+      </c>
+      <c r="K7" s="55">
+        <v>1</v>
+      </c>
+      <c r="L7" s="55">
+        <v>1</v>
+      </c>
+      <c r="M7" s="55">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="55">
+        <v>0</v>
+      </c>
+      <c r="P7" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="55">
+        <v>1</v>
+      </c>
+      <c r="R7" s="55">
+        <v>0</v>
+      </c>
+      <c r="S7" s="55">
+        <v>0</v>
+      </c>
+      <c r="T7" s="55">
+        <v>0</v>
+      </c>
+      <c r="U7" s="55">
+        <v>0</v>
+      </c>
+      <c r="V7" s="55">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="55">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="55">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="55">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="55">
+        <v>2.5</v>
+      </c>
+      <c r="AE7" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="55">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="55">
+        <v>1.8333333329999999</v>
+      </c>
+      <c r="AH7" s="55"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A8" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="53">
+        <v>6</v>
+      </c>
+      <c r="D8" s="53">
+        <v>1</v>
+      </c>
+      <c r="E8" s="53">
+        <v>0</v>
+      </c>
+      <c r="F8" s="53">
+        <v>2</v>
+      </c>
+      <c r="G8" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="55">
+        <v>4</v>
+      </c>
+      <c r="J8" s="55">
+        <v>1</v>
+      </c>
+      <c r="K8" s="55">
+        <v>1</v>
+      </c>
+      <c r="L8" s="55">
+        <v>1</v>
+      </c>
+      <c r="M8" s="55">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="55">
+        <v>1</v>
+      </c>
+      <c r="P8" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="55">
+        <v>1</v>
+      </c>
+      <c r="R8" s="55">
+        <v>1</v>
+      </c>
+      <c r="S8" s="55">
+        <v>0</v>
+      </c>
+      <c r="T8" s="55">
+        <v>1</v>
+      </c>
+      <c r="U8" s="55">
+        <v>0</v>
+      </c>
+      <c r="V8" s="55">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="55">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="55">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="55">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="55">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="55">
+        <v>5</v>
+      </c>
+      <c r="AE8" s="55">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="55">
+        <v>3</v>
+      </c>
+      <c r="AH8" s="55"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A9" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="53">
+        <v>7</v>
+      </c>
+      <c r="D9" s="53">
+        <v>1</v>
+      </c>
+      <c r="E9" s="53">
+        <v>0</v>
+      </c>
+      <c r="F9" s="53">
+        <v>2</v>
+      </c>
+      <c r="G9" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="I9" s="55">
+        <v>4</v>
+      </c>
+      <c r="J9" s="55">
+        <v>1</v>
+      </c>
+      <c r="K9" s="55">
+        <v>1</v>
+      </c>
+      <c r="L9" s="55">
+        <v>1</v>
+      </c>
+      <c r="M9" s="55">
+        <v>1</v>
+      </c>
+      <c r="N9" s="55">
+        <v>1</v>
+      </c>
+      <c r="O9" s="55">
+        <v>1</v>
+      </c>
+      <c r="P9" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="55">
+        <v>1</v>
+      </c>
+      <c r="R9" s="55">
+        <v>1</v>
+      </c>
+      <c r="S9" s="55">
+        <v>0</v>
+      </c>
+      <c r="T9" s="55">
+        <v>0</v>
+      </c>
+      <c r="U9" s="55">
+        <v>0</v>
+      </c>
+      <c r="V9" s="55">
+        <v>0</v>
+      </c>
+      <c r="W9" s="55">
+        <v>0</v>
+      </c>
+      <c r="X9" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="55">
+        <v>6</v>
+      </c>
+      <c r="AA9" s="55">
+        <v>2</v>
+      </c>
+      <c r="AB9" s="55">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="55">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="55">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="55">
+        <v>2</v>
+      </c>
+      <c r="AF9" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="55">
+        <v>2.6666666669999999</v>
+      </c>
+      <c r="AH9" s="55"/>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A10" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="53">
+        <v>8</v>
+      </c>
+      <c r="D10" s="53">
+        <v>0</v>
+      </c>
+      <c r="E10" s="53">
+        <v>0</v>
+      </c>
+      <c r="F10" s="53">
+        <v>1</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" s="55">
+        <v>1</v>
+      </c>
+      <c r="J10" s="55">
+        <v>1</v>
+      </c>
+      <c r="K10" s="55">
+        <v>1</v>
+      </c>
+      <c r="L10" s="55">
+        <v>1</v>
+      </c>
+      <c r="M10" s="55">
+        <v>0</v>
+      </c>
+      <c r="N10" s="55">
+        <v>0</v>
+      </c>
+      <c r="O10" s="55">
+        <v>0</v>
+      </c>
+      <c r="P10" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="55">
+        <v>1</v>
+      </c>
+      <c r="R10" s="55">
+        <v>0</v>
+      </c>
+      <c r="S10" s="55">
+        <v>0</v>
+      </c>
+      <c r="T10" s="55">
+        <v>0</v>
+      </c>
+      <c r="U10" s="55">
+        <v>0</v>
+      </c>
+      <c r="V10" s="55">
+        <v>0</v>
+      </c>
+      <c r="W10" s="55">
+        <v>0</v>
+      </c>
+      <c r="X10" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="55">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="55">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="55">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="55">
+        <v>2.5</v>
+      </c>
+      <c r="AE10" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="55">
+        <v>1.5</v>
+      </c>
+      <c r="AH10" s="55"/>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A11" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="53">
+        <v>9</v>
+      </c>
+      <c r="D11" s="53">
+        <v>0</v>
+      </c>
+      <c r="E11" s="53">
+        <v>0</v>
+      </c>
+      <c r="F11" s="53">
+        <v>1</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="55">
+        <v>2</v>
+      </c>
+      <c r="J11" s="55">
+        <v>1</v>
+      </c>
+      <c r="K11" s="55">
+        <v>1</v>
+      </c>
+      <c r="L11" s="55">
+        <v>1</v>
+      </c>
+      <c r="M11" s="55">
+        <v>0</v>
+      </c>
+      <c r="N11" s="55">
+        <v>0</v>
+      </c>
+      <c r="O11" s="55">
+        <v>0</v>
+      </c>
+      <c r="P11" s="55">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="55">
+        <v>1</v>
+      </c>
+      <c r="R11" s="55">
+        <v>0</v>
+      </c>
+      <c r="S11" s="55">
+        <v>0</v>
+      </c>
+      <c r="T11" s="55">
+        <v>0</v>
+      </c>
+      <c r="U11" s="55">
+        <v>0</v>
+      </c>
+      <c r="V11" s="55">
+        <v>0</v>
+      </c>
+      <c r="W11" s="55">
+        <v>0</v>
+      </c>
+      <c r="X11" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="55">
+        <v>3</v>
+      </c>
+      <c r="AA11" s="55">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="55">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="55">
+        <v>6</v>
+      </c>
+      <c r="AD11" s="55">
+        <v>2.5</v>
+      </c>
+      <c r="AE11" s="55">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="55">
+        <v>1.8333333329999999</v>
+      </c>
+      <c r="AH11" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A12" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="53">
+        <v>10</v>
+      </c>
+      <c r="D12" s="53">
+        <v>0</v>
+      </c>
+      <c r="E12" s="53">
+        <v>0</v>
+      </c>
+      <c r="F12" s="53">
+        <v>2</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" s="55">
+        <v>2</v>
+      </c>
+      <c r="J12" s="55">
+        <v>1</v>
+      </c>
+      <c r="K12" s="55">
+        <v>0</v>
+      </c>
+      <c r="L12" s="55">
+        <v>0</v>
+      </c>
+      <c r="M12" s="55">
+        <v>1</v>
+      </c>
+      <c r="N12" s="55">
+        <v>1</v>
+      </c>
+      <c r="O12" s="55">
+        <v>0</v>
+      </c>
+      <c r="P12" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="55">
+        <v>0</v>
+      </c>
+      <c r="R12" s="55">
+        <v>0</v>
+      </c>
+      <c r="S12" s="55">
+        <v>0</v>
+      </c>
+      <c r="T12" s="55">
+        <v>0</v>
+      </c>
+      <c r="U12" s="55">
+        <v>0</v>
+      </c>
+      <c r="V12" s="55">
+        <v>0</v>
+      </c>
+      <c r="W12" s="55">
+        <v>0</v>
+      </c>
+      <c r="X12" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="55">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="55">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="55">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="55">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="55">
+        <v>2.5</v>
+      </c>
+      <c r="AE12" s="55">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="55">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="55">
+        <v>1.5</v>
+      </c>
+      <c r="AH12" s="55"/>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A13" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="56">
+        <v>11</v>
+      </c>
+      <c r="D13" s="56">
+        <v>0</v>
+      </c>
+      <c r="E13" s="56">
+        <v>0</v>
+      </c>
+      <c r="F13" s="56">
+        <v>0</v>
+      </c>
+      <c r="G13" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="58">
+        <v>0</v>
+      </c>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
+      <c r="V13" s="58"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="58"/>
+      <c r="Y13" s="59"/>
+      <c r="Z13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="58">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="58"/>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A14" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="53">
+        <v>12</v>
+      </c>
+      <c r="D14" s="53">
+        <v>1</v>
+      </c>
+      <c r="E14" s="53">
+        <v>0</v>
+      </c>
+      <c r="F14" s="53">
+        <v>2</v>
+      </c>
+      <c r="G14" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" s="55">
+        <v>2</v>
+      </c>
+      <c r="J14" s="55">
+        <v>1</v>
+      </c>
+      <c r="K14" s="55">
+        <v>1</v>
+      </c>
+      <c r="L14" s="55">
+        <v>1</v>
+      </c>
+      <c r="M14" s="55">
+        <v>0</v>
+      </c>
+      <c r="N14" s="55">
+        <v>1</v>
+      </c>
+      <c r="O14" s="55">
+        <v>0</v>
+      </c>
+      <c r="P14" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="55">
+        <v>0</v>
+      </c>
+      <c r="R14" s="55">
+        <v>0</v>
+      </c>
+      <c r="S14" s="55">
+        <v>0</v>
+      </c>
+      <c r="T14" s="55">
+        <v>0</v>
+      </c>
+      <c r="U14" s="55">
+        <v>1</v>
+      </c>
+      <c r="V14" s="55">
+        <v>0</v>
+      </c>
+      <c r="W14" s="55">
+        <v>1</v>
+      </c>
+      <c r="X14" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="55">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="55">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="55">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="55">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="55">
+        <v>3.3333333330000001</v>
+      </c>
+      <c r="AE14" s="55">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="55">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="55">
+        <v>2.4444444440000002</v>
+      </c>
+      <c r="AH14" s="55"/>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A15" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="53">
+        <v>13</v>
+      </c>
+      <c r="D15" s="53">
+        <v>1</v>
+      </c>
+      <c r="E15" s="53">
+        <v>0</v>
+      </c>
+      <c r="F15" s="53">
+        <v>2</v>
+      </c>
+      <c r="G15" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="55">
+        <v>4</v>
+      </c>
+      <c r="J15" s="55">
+        <v>1</v>
+      </c>
+      <c r="K15" s="55">
+        <v>1</v>
+      </c>
+      <c r="L15" s="55">
+        <v>1</v>
+      </c>
+      <c r="M15" s="55">
+        <v>1</v>
+      </c>
+      <c r="N15" s="55">
+        <v>1</v>
+      </c>
+      <c r="O15" s="55">
+        <v>1</v>
+      </c>
+      <c r="P15" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="55">
+        <v>1</v>
+      </c>
+      <c r="R15" s="55">
+        <v>1</v>
+      </c>
+      <c r="S15" s="55">
+        <v>0</v>
+      </c>
+      <c r="T15" s="55">
+        <v>0</v>
+      </c>
+      <c r="U15" s="55">
+        <v>1</v>
+      </c>
+      <c r="V15" s="55">
+        <v>1</v>
+      </c>
+      <c r="W15" s="55">
+        <v>1</v>
+      </c>
+      <c r="X15" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="55">
+        <v>6</v>
+      </c>
+      <c r="AA15" s="55">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="55">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="55">
+        <v>12</v>
+      </c>
+      <c r="AD15" s="55">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="55">
+        <v>2</v>
+      </c>
+      <c r="AF15" s="55">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="55">
+        <v>3.6666666669999999</v>
+      </c>
+      <c r="AH15" s="55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A16" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="53">
+        <v>14</v>
+      </c>
+      <c r="D16" s="53">
+        <v>1</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0</v>
+      </c>
+      <c r="F16" s="53">
+        <v>2</v>
+      </c>
+      <c r="G16" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="H16" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="I16" s="55">
+        <v>2</v>
+      </c>
+      <c r="J16" s="55">
+        <v>1</v>
+      </c>
+      <c r="K16" s="55">
+        <v>0</v>
+      </c>
+      <c r="L16" s="55">
+        <v>0</v>
+      </c>
+      <c r="M16" s="55">
+        <v>0</v>
+      </c>
+      <c r="N16" s="55">
+        <v>1</v>
+      </c>
+      <c r="O16" s="55">
+        <v>0</v>
+      </c>
+      <c r="P16" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="55">
+        <v>0</v>
+      </c>
+      <c r="R16" s="55">
+        <v>0</v>
+      </c>
+      <c r="S16" s="55">
+        <v>0</v>
+      </c>
+      <c r="T16" s="55">
+        <v>0</v>
+      </c>
+      <c r="U16" s="55">
+        <v>1</v>
+      </c>
+      <c r="V16" s="55">
+        <v>1</v>
+      </c>
+      <c r="W16" s="55">
+        <v>1</v>
+      </c>
+      <c r="X16" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="55">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="55">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="55">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="55">
+        <v>6</v>
+      </c>
+      <c r="AD16" s="55">
+        <v>1.6666666670000001</v>
+      </c>
+      <c r="AE16" s="55">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="55">
+        <v>4</v>
+      </c>
+      <c r="AG16" s="55">
+        <v>1.888888889</v>
+      </c>
+      <c r="AH16" s="55"/>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A17" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="53">
+        <v>15</v>
+      </c>
+      <c r="D17" s="53">
+        <v>1</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0</v>
+      </c>
+      <c r="F17" s="53">
+        <v>2</v>
+      </c>
+      <c r="G17" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="55">
+        <v>3</v>
+      </c>
+      <c r="J17" s="55">
+        <v>1</v>
+      </c>
+      <c r="K17" s="55">
+        <v>1</v>
+      </c>
+      <c r="L17" s="55">
+        <v>0</v>
+      </c>
+      <c r="M17" s="55">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2">
+        <v>1</v>
+      </c>
+      <c r="O17" s="55">
+        <v>0</v>
+      </c>
+      <c r="P17" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2">
+        <v>1</v>
+      </c>
+      <c r="S17" s="55">
+        <v>0</v>
+      </c>
+      <c r="T17" s="55">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="55">
+        <v>1</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="55">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="55">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="55">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="55">
+        <v>8</v>
+      </c>
+      <c r="AD17" s="55">
+        <v>3.3333333330000001</v>
+      </c>
+      <c r="AE17" s="55">
+        <v>2</v>
+      </c>
+      <c r="AF17" s="55">
+        <v>2</v>
+      </c>
+      <c r="AG17" s="55">
+        <v>2.4444444440000002</v>
+      </c>
+      <c r="AH17" s="55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A18" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" s="53">
+        <v>16</v>
+      </c>
+      <c r="D18" s="53">
+        <v>0</v>
+      </c>
+      <c r="E18" s="53">
+        <v>0</v>
+      </c>
+      <c r="F18" s="53">
+        <v>1</v>
+      </c>
+      <c r="G18" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" s="55">
+        <v>1</v>
+      </c>
+      <c r="J18" s="55">
+        <v>1</v>
+      </c>
+      <c r="K18" s="55">
+        <v>0</v>
+      </c>
+      <c r="L18" s="55">
+        <v>0</v>
+      </c>
+      <c r="M18" s="55">
+        <v>0</v>
+      </c>
+      <c r="N18" s="55">
+        <v>0</v>
+      </c>
+      <c r="O18" s="55">
+        <v>0</v>
+      </c>
+      <c r="P18" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="55">
+        <v>1</v>
+      </c>
+      <c r="R18" s="55">
+        <v>0</v>
+      </c>
+      <c r="S18" s="55">
+        <v>0</v>
+      </c>
+      <c r="T18" s="55">
+        <v>0</v>
+      </c>
+      <c r="U18" s="55">
+        <v>0</v>
+      </c>
+      <c r="V18" s="55">
+        <v>0</v>
+      </c>
+      <c r="W18" s="55">
+        <v>0</v>
+      </c>
+      <c r="X18" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="55">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="55">
+        <v>2</v>
+      </c>
+      <c r="AC18" s="55">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="55">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="AE18" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="55">
+        <v>2</v>
+      </c>
+      <c r="AG18" s="55">
+        <v>1.2777777779999999</v>
+      </c>
+      <c r="AH18" s="55"/>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A19" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="53">
+        <v>17</v>
+      </c>
+      <c r="D19" s="53">
+        <v>0</v>
+      </c>
+      <c r="E19" s="53">
+        <v>0</v>
+      </c>
+      <c r="F19" s="53">
+        <v>1</v>
+      </c>
+      <c r="G19" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="I19" s="55">
+        <v>1</v>
+      </c>
+      <c r="J19" s="55">
+        <v>1</v>
+      </c>
+      <c r="K19" s="55">
+        <v>0</v>
+      </c>
+      <c r="L19" s="55">
+        <v>0</v>
+      </c>
+      <c r="M19" s="55">
+        <v>0</v>
+      </c>
+      <c r="N19" s="55">
+        <v>0</v>
+      </c>
+      <c r="O19" s="55">
+        <v>0</v>
+      </c>
+      <c r="P19" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="55">
+        <v>1</v>
+      </c>
+      <c r="R19" s="55">
+        <v>0</v>
+      </c>
+      <c r="S19" s="55">
+        <v>0</v>
+      </c>
+      <c r="T19" s="55">
+        <v>0</v>
+      </c>
+      <c r="U19" s="55">
+        <v>0</v>
+      </c>
+      <c r="V19" s="55">
+        <v>0</v>
+      </c>
+      <c r="W19" s="55">
+        <v>0</v>
+      </c>
+      <c r="X19" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="55">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="55">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="55">
+        <v>3</v>
+      </c>
+      <c r="AD19" s="55">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="AE19" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="55">
+        <v>0.94444444400000005</v>
+      </c>
+      <c r="AH19" s="55"/>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A20" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="53">
+        <v>18</v>
+      </c>
+      <c r="D20" s="53">
+        <v>0</v>
+      </c>
+      <c r="E20" s="53">
+        <v>0</v>
+      </c>
+      <c r="F20" s="53">
+        <v>1</v>
+      </c>
+      <c r="G20" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="55">
+        <v>1</v>
+      </c>
+      <c r="J20" s="55">
+        <v>1</v>
+      </c>
+      <c r="K20" s="55">
+        <v>0</v>
+      </c>
+      <c r="L20" s="55">
+        <v>0</v>
+      </c>
+      <c r="M20" s="55">
+        <v>0</v>
+      </c>
+      <c r="N20" s="55">
+        <v>0</v>
+      </c>
+      <c r="O20" s="55">
+        <v>0</v>
+      </c>
+      <c r="P20" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="55">
+        <v>1</v>
+      </c>
+      <c r="R20" s="55">
+        <v>0</v>
+      </c>
+      <c r="S20" s="55">
+        <v>0</v>
+      </c>
+      <c r="T20" s="55">
+        <v>0</v>
+      </c>
+      <c r="U20" s="55">
+        <v>0</v>
+      </c>
+      <c r="V20" s="55">
+        <v>0</v>
+      </c>
+      <c r="W20" s="55">
+        <v>0</v>
+      </c>
+      <c r="X20" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="55">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="55">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="55">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="55">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="AE20" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="55">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="55">
+        <v>1.2777777779999999</v>
+      </c>
+      <c r="AH20" s="55"/>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A21" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="53">
+        <v>19</v>
+      </c>
+      <c r="D21" s="53">
+        <v>0</v>
+      </c>
+      <c r="E21" s="53">
+        <v>0</v>
+      </c>
+      <c r="F21" s="53">
+        <v>1</v>
+      </c>
+      <c r="G21" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="55">
+        <v>2</v>
+      </c>
+      <c r="J21" s="55">
+        <v>1</v>
+      </c>
+      <c r="K21" s="55">
+        <v>1</v>
+      </c>
+      <c r="L21" s="55">
+        <v>0</v>
+      </c>
+      <c r="M21" s="55">
+        <v>0</v>
+      </c>
+      <c r="N21" s="55">
+        <v>0</v>
+      </c>
+      <c r="O21" s="55">
+        <v>0</v>
+      </c>
+      <c r="P21" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="55">
+        <v>1</v>
+      </c>
+      <c r="R21" s="55">
+        <v>0</v>
+      </c>
+      <c r="S21" s="55">
+        <v>0</v>
+      </c>
+      <c r="T21" s="55">
+        <v>0</v>
+      </c>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55">
+        <v>0</v>
+      </c>
+      <c r="W21" s="55">
+        <v>0</v>
+      </c>
+      <c r="X21" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="55">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="55">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="55">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="55">
+        <v>1.6666666670000001</v>
+      </c>
+      <c r="AE21" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="55">
+        <v>2</v>
+      </c>
+      <c r="AG21" s="55">
+        <v>1.5555555560000001</v>
+      </c>
+      <c r="AH21" s="55"/>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A22" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="53">
+        <v>20</v>
+      </c>
+      <c r="D22" s="53">
+        <v>0</v>
+      </c>
+      <c r="E22" s="53">
+        <v>0</v>
+      </c>
+      <c r="F22" s="53">
+        <v>1</v>
+      </c>
+      <c r="G22" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="55">
+        <v>2</v>
+      </c>
+      <c r="J22" s="55">
+        <v>1</v>
+      </c>
+      <c r="K22" s="55">
+        <v>1</v>
+      </c>
+      <c r="L22" s="55">
+        <v>0</v>
+      </c>
+      <c r="M22" s="55">
+        <v>1</v>
+      </c>
+      <c r="N22" s="55">
+        <v>0</v>
+      </c>
+      <c r="O22" s="55">
+        <v>0</v>
+      </c>
+      <c r="P22" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="55">
+        <v>1</v>
+      </c>
+      <c r="R22" s="55">
+        <v>0</v>
+      </c>
+      <c r="S22" s="55">
+        <v>0</v>
+      </c>
+      <c r="T22" s="55">
+        <v>0</v>
+      </c>
+      <c r="U22" s="55">
+        <v>0</v>
+      </c>
+      <c r="V22" s="55">
+        <v>0</v>
+      </c>
+      <c r="W22" s="55">
+        <v>0</v>
+      </c>
+      <c r="X22" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="55">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="55">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="55">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="55">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="55">
+        <v>2.5</v>
+      </c>
+      <c r="AE22" s="55">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="55">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="55">
+        <v>1.5</v>
+      </c>
+      <c r="AH22" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2112888-7973-47DC-A544-A7D66FB94C5B}">
   <dimension ref="A1:AF87"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -15390,28 +17670,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="71.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
+      <c r="G1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
       <c r="W1" s="20"/>
       <c r="X1" s="20"/>
     </row>
@@ -15731,10 +18011,10 @@
       <c r="AF5" s="4"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="67">
         <v>1</v>
       </c>
       <c r="D6" s="22"/>
@@ -15827,8 +18107,8 @@
       <c r="AF6" s="4"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
       <c r="D7" s="22"/>
       <c r="E7" s="3" t="s">
         <v>48</v>
@@ -15920,10 +18200,10 @@
       <c r="AF7" s="4"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="67">
         <v>2</v>
       </c>
       <c r="D8" s="22"/>
@@ -15966,8 +18246,8 @@
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
       <c r="D9" s="22"/>
       <c r="E9" s="3" t="s">
         <v>48</v>
@@ -16010,10 +18290,10 @@
       <c r="AF9" s="4"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="67">
         <v>3</v>
       </c>
       <c r="D10" s="22"/>
@@ -16106,8 +18386,8 @@
       <c r="AF10" s="6"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
       <c r="D11" s="22"/>
       <c r="E11" s="3" t="s">
         <v>48</v>
@@ -16198,10 +18478,10 @@
       <c r="AF11" s="4"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="67">
         <v>4</v>
       </c>
       <c r="D12" s="22"/>
@@ -16294,8 +18574,8 @@
       <c r="AF12" s="4"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="22"/>
       <c r="E13" s="3" t="s">
         <v>48</v>
@@ -16386,10 +18666,10 @@
       <c r="AF13" s="4"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="59">
+      <c r="C14" s="67">
         <v>5</v>
       </c>
       <c r="D14" s="22"/>
@@ -16482,8 +18762,8 @@
       <c r="AF14" s="5"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
       <c r="D15" s="22"/>
       <c r="E15" s="3" t="s">
         <v>48</v>
@@ -16574,10 +18854,10 @@
       <c r="AF15" s="4"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="67">
         <v>6</v>
       </c>
       <c r="D16" s="22"/>
@@ -16670,8 +18950,8 @@
       <c r="AF16" s="4"/>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
       <c r="D17" s="22"/>
       <c r="E17" s="3" t="s">
         <v>48</v>
@@ -16762,10 +19042,10 @@
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="59">
+      <c r="C18" s="67">
         <v>15</v>
       </c>
       <c r="D18" s="22"/>
@@ -16857,8 +19137,8 @@
       </c>
     </row>
     <row r="19" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
       <c r="D19" s="22"/>
       <c r="E19" s="3" t="s">
         <v>48</v>
@@ -16948,10 +19228,10 @@
       </c>
     </row>
     <row r="20" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="59">
+      <c r="C20" s="67">
         <v>16</v>
       </c>
       <c r="D20" s="22"/>
@@ -17043,8 +19323,8 @@
       </c>
     </row>
     <row r="21" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="22"/>
       <c r="E21" s="3" t="s">
         <v>48</v>
@@ -17134,10 +19414,10 @@
       </c>
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="67">
         <v>17</v>
       </c>
       <c r="D22" s="22"/>
@@ -17229,8 +19509,8 @@
       </c>
     </row>
     <row r="23" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="22"/>
       <c r="E23" s="3" t="s">
         <v>48</v>
@@ -17320,10 +19600,10 @@
       </c>
     </row>
     <row r="24" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="67">
         <v>18</v>
       </c>
       <c r="D24" s="22"/>
@@ -17415,8 +19695,8 @@
       </c>
     </row>
     <row r="25" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
       <c r="D25" s="22"/>
       <c r="E25" s="3" t="s">
         <v>48</v>
@@ -17506,10 +19786,10 @@
       </c>
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="59">
+      <c r="C26" s="67">
         <v>19</v>
       </c>
       <c r="D26" s="22"/>
@@ -17601,8 +19881,8 @@
       </c>
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
       <c r="D27" s="22"/>
       <c r="E27" s="3" t="s">
         <v>48</v>
@@ -17692,10 +19972,10 @@
       </c>
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="59">
+      <c r="C28" s="67">
         <v>7</v>
       </c>
       <c r="D28" s="22"/>
@@ -17787,8 +20067,8 @@
       </c>
     </row>
     <row r="29" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B29" s="59"/>
-      <c r="C29" s="59"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
       <c r="D29" s="22"/>
       <c r="E29" s="3" t="s">
         <v>48</v>
@@ -17878,10 +20158,10 @@
       </c>
     </row>
     <row r="30" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="C30" s="59">
+      <c r="C30" s="67">
         <v>8</v>
       </c>
       <c r="D30" s="22"/>
@@ -17925,8 +20205,8 @@
       </c>
     </row>
     <row r="31" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
       <c r="D31" s="22"/>
       <c r="E31" s="3" t="s">
         <v>48</v>
@@ -18016,10 +20296,10 @@
       </c>
     </row>
     <row r="32" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="C32" s="59">
+      <c r="C32" s="67">
         <v>9</v>
       </c>
       <c r="D32" s="22"/>
@@ -18063,8 +20343,8 @@
       </c>
     </row>
     <row r="33" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B33" s="59"/>
-      <c r="C33" s="59"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
       <c r="D33" s="22"/>
       <c r="E33" s="3" t="s">
         <v>48</v>
@@ -18154,10 +20434,10 @@
       </c>
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B34" s="59" t="s">
+      <c r="B34" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="C34" s="59">
+      <c r="C34" s="67">
         <v>10</v>
       </c>
       <c r="D34" s="22"/>
@@ -18249,8 +20529,8 @@
       </c>
     </row>
     <row r="35" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B35" s="59"/>
-      <c r="C35" s="59"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
       <c r="D35" s="22"/>
       <c r="E35" s="3" t="s">
         <v>48</v>
@@ -18340,10 +20620,10 @@
       </c>
     </row>
     <row r="36" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="67">
         <v>11</v>
       </c>
       <c r="D36" s="22"/>
@@ -18435,8 +20715,8 @@
       </c>
     </row>
     <row r="37" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B37" s="59"/>
-      <c r="C37" s="59"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
       <c r="D37" s="22"/>
       <c r="E37" s="3" t="s">
         <v>48</v>
@@ -18526,10 +20806,10 @@
       </c>
     </row>
     <row r="38" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="67">
         <v>12</v>
       </c>
       <c r="D38" s="22"/>
@@ -18621,8 +20901,8 @@
       </c>
     </row>
     <row r="39" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
       <c r="D39" s="22"/>
       <c r="E39" s="3" t="s">
         <v>48</v>
@@ -18712,10 +20992,10 @@
       </c>
     </row>
     <row r="40" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="C40" s="59">
+      <c r="C40" s="67">
         <v>13</v>
       </c>
       <c r="D40" s="22"/>
@@ -18759,8 +21039,8 @@
       </c>
     </row>
     <row r="41" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
       <c r="D41" s="22"/>
       <c r="E41" s="3" t="s">
         <v>48</v>
@@ -18850,10 +21130,10 @@
       </c>
     </row>
     <row r="42" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="C42" s="59">
+      <c r="C42" s="67">
         <v>14</v>
       </c>
       <c r="D42" s="22"/>
@@ -18945,8 +21225,8 @@
       </c>
     </row>
     <row r="43" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67"/>
       <c r="D43" s="22"/>
       <c r="E43" s="3" t="s">
         <v>48</v>
@@ -19036,8 +21316,8 @@
       </c>
     </row>
     <row r="44" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B44" s="59"/>
-      <c r="C44" s="59"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="67"/>
       <c r="D44" s="22"/>
       <c r="W44" s="1">
         <f t="shared" si="16"/>
@@ -19073,8 +21353,8 @@
       </c>
     </row>
     <row r="45" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B45" s="59"/>
-      <c r="C45" s="59"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="67"/>
       <c r="D45" s="22"/>
       <c r="W45" s="1">
         <f t="shared" si="16"/>
@@ -19110,17 +21390,17 @@
       </c>
     </row>
     <row r="46" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B46" s="60" t="s">
+      <c r="B46" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59" t="s">
+      <c r="C46" s="67"/>
+      <c r="D46" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="59"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="67"/>
       <c r="W46" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -19155,13 +21435,13 @@
       </c>
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B47" s="59"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
       <c r="W47" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -19196,8 +21476,8 @@
       </c>
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B48" s="59"/>
-      <c r="C48" s="59"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
       <c r="D48" s="22"/>
       <c r="W48" s="1">
         <f t="shared" si="16"/>
@@ -19233,8 +21513,8 @@
       </c>
     </row>
     <row r="49" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B49" s="59"/>
-      <c r="C49" s="59"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="67"/>
       <c r="D49" s="22"/>
       <c r="W49" s="1">
         <f t="shared" si="16"/>
@@ -19270,10 +21550,10 @@
       </c>
     </row>
     <row r="50" spans="2:32" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="C50" s="59">
+      <c r="C50" s="67">
         <v>1</v>
       </c>
       <c r="D50" s="30"/>
@@ -19366,8 +21646,8 @@
       <c r="AF50" s="34"/>
     </row>
     <row r="51" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B51" s="59"/>
-      <c r="C51" s="59"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="67"/>
       <c r="D51" s="22"/>
       <c r="E51" s="3" t="s">
         <v>48</v>
@@ -19459,10 +21739,10 @@
       <c r="AF51" s="4"/>
     </row>
     <row r="52" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B52" s="61" t="s">
+      <c r="B52" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="61">
+      <c r="C52" s="69">
         <v>2</v>
       </c>
       <c r="D52" s="22"/>
@@ -19505,8 +21785,8 @@
       <c r="AF52" s="4"/>
     </row>
     <row r="53" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="69"/>
       <c r="D53" s="22"/>
       <c r="E53" s="3" t="s">
         <v>48</v>
@@ -19549,10 +21829,10 @@
       <c r="AF53" s="4"/>
     </row>
     <row r="54" spans="2:32" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="59" t="s">
+      <c r="B54" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="C54" s="59">
+      <c r="C54" s="67">
         <v>3</v>
       </c>
       <c r="D54" s="25"/>
@@ -19645,8 +21925,8 @@
       <c r="AF54" s="28"/>
     </row>
     <row r="55" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
       <c r="D55" s="22"/>
       <c r="E55" s="3" t="s">
         <v>48</v>
@@ -19737,10 +22017,10 @@
       <c r="AF55" s="4"/>
     </row>
     <row r="56" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B56" s="59" t="s">
+      <c r="B56" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="59">
+      <c r="C56" s="67">
         <v>4</v>
       </c>
       <c r="D56" s="22"/>
@@ -19833,8 +22113,8 @@
       <c r="AF56" s="4"/>
     </row>
     <row r="57" spans="2:32" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="59"/>
-      <c r="C57" s="59"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="67"/>
       <c r="D57" s="25"/>
       <c r="E57" s="23" t="s">
         <v>48</v>
@@ -19925,10 +22205,10 @@
       <c r="AF57" s="27"/>
     </row>
     <row r="58" spans="2:32" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="59">
+      <c r="C58" s="67">
         <v>5</v>
       </c>
       <c r="D58" s="25"/>
@@ -20021,8 +22301,8 @@
       <c r="AF58" s="29"/>
     </row>
     <row r="59" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B59" s="59"/>
-      <c r="C59" s="59"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="67"/>
       <c r="D59" s="22"/>
       <c r="E59" s="3" t="s">
         <v>48</v>
@@ -20113,10 +22393,10 @@
       <c r="AF59" s="4"/>
     </row>
     <row r="60" spans="2:32" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="59" t="s">
+      <c r="B60" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="C60" s="59">
+      <c r="C60" s="67">
         <v>6</v>
       </c>
       <c r="D60" s="30"/>
@@ -20209,8 +22489,8 @@
       <c r="AF60" s="34"/>
     </row>
     <row r="61" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B61" s="59"/>
-      <c r="C61" s="59"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="67"/>
       <c r="D61" s="22"/>
       <c r="E61" s="3" t="s">
         <v>48</v>
@@ -20301,10 +22581,10 @@
       <c r="AF61" s="4"/>
     </row>
     <row r="62" spans="2:32" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="59" t="s">
+      <c r="B62" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="C62" s="59">
+      <c r="C62" s="67">
         <v>15</v>
       </c>
       <c r="D62" s="30"/>
@@ -20396,8 +22676,8 @@
       </c>
     </row>
     <row r="63" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B63" s="59"/>
-      <c r="C63" s="59"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="67"/>
       <c r="D63" s="22"/>
       <c r="E63" s="3" t="s">
         <v>48</v>
@@ -20487,10 +22767,10 @@
       </c>
     </row>
     <row r="64" spans="2:32" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="59" t="s">
+      <c r="B64" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="C64" s="59">
+      <c r="C64" s="67">
         <v>16</v>
       </c>
       <c r="D64" s="25"/>
@@ -20582,8 +22862,8 @@
       </c>
     </row>
     <row r="65" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B65" s="59"/>
-      <c r="C65" s="59"/>
+      <c r="B65" s="67"/>
+      <c r="C65" s="67"/>
       <c r="D65" s="22"/>
       <c r="E65" s="3" t="s">
         <v>48</v>
@@ -20673,10 +22953,10 @@
       </c>
     </row>
     <row r="66" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B66" s="59" t="s">
+      <c r="B66" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="C66" s="59">
+      <c r="C66" s="67">
         <v>17</v>
       </c>
       <c r="D66" s="22"/>
@@ -20768,8 +23048,8 @@
       </c>
     </row>
     <row r="67" spans="2:30" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="59"/>
-      <c r="C67" s="59"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="67"/>
       <c r="D67" s="25"/>
       <c r="E67" s="23" t="s">
         <v>48</v>
@@ -20859,10 +23139,10 @@
       </c>
     </row>
     <row r="68" spans="2:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="59" t="s">
+      <c r="B68" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="C68" s="59">
+      <c r="C68" s="67">
         <v>18</v>
       </c>
       <c r="D68" s="30"/>
@@ -20954,8 +23234,8 @@
       </c>
     </row>
     <row r="69" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B69" s="59"/>
-      <c r="C69" s="59"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67"/>
       <c r="D69" s="22"/>
       <c r="E69" s="3" t="s">
         <v>48</v>
@@ -21045,10 +23325,10 @@
       </c>
     </row>
     <row r="70" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B70" s="59" t="s">
+      <c r="B70" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="C70" s="59">
+      <c r="C70" s="67">
         <v>19</v>
       </c>
       <c r="D70" s="22"/>
@@ -21140,8 +23420,8 @@
       </c>
     </row>
     <row r="71" spans="2:30" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="59"/>
-      <c r="C71" s="59"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="67"/>
       <c r="D71" s="25"/>
       <c r="E71" s="23" t="s">
         <v>48</v>
@@ -21231,10 +23511,10 @@
       </c>
     </row>
     <row r="72" spans="2:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="59" t="s">
+      <c r="B72" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="C72" s="59">
+      <c r="C72" s="67">
         <v>7</v>
       </c>
       <c r="D72" s="30"/>
@@ -21326,8 +23606,8 @@
       </c>
     </row>
     <row r="73" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B73" s="59"/>
-      <c r="C73" s="59"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="67"/>
       <c r="D73" s="22"/>
       <c r="E73" s="3" t="s">
         <v>48</v>
@@ -21417,10 +23697,10 @@
       </c>
     </row>
     <row r="74" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B74" s="59" t="s">
+      <c r="B74" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="C74" s="59">
+      <c r="C74" s="67">
         <v>8</v>
       </c>
       <c r="D74" s="22"/>
@@ -21464,8 +23744,8 @@
       </c>
     </row>
     <row r="75" spans="2:30" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="59"/>
-      <c r="C75" s="59"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="67"/>
       <c r="D75" s="25"/>
       <c r="E75" s="23" t="s">
         <v>48</v>
@@ -21555,10 +23835,10 @@
       </c>
     </row>
     <row r="76" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B76" s="59" t="s">
+      <c r="B76" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="C76" s="59">
+      <c r="C76" s="67">
         <v>9</v>
       </c>
       <c r="D76" s="22"/>
@@ -21602,8 +23882,8 @@
       </c>
     </row>
     <row r="77" spans="2:30" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="59"/>
-      <c r="C77" s="59"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="67"/>
       <c r="D77" s="25"/>
       <c r="E77" s="23" t="s">
         <v>48</v>
@@ -21693,10 +23973,10 @@
       </c>
     </row>
     <row r="78" spans="2:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="C78" s="59">
+      <c r="C78" s="67">
         <v>10</v>
       </c>
       <c r="D78" s="30"/>
@@ -21788,8 +24068,8 @@
       </c>
     </row>
     <row r="79" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B79" s="59"/>
-      <c r="C79" s="59"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="67"/>
       <c r="D79" s="22"/>
       <c r="E79" s="3" t="s">
         <v>48</v>
@@ -21879,10 +24159,10 @@
       </c>
     </row>
     <row r="80" spans="2:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="59" t="s">
+      <c r="B80" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="C80" s="59">
+      <c r="C80" s="67">
         <v>11</v>
       </c>
       <c r="D80" s="30"/>
@@ -21974,8 +24254,8 @@
       </c>
     </row>
     <row r="81" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B81" s="59"/>
-      <c r="C81" s="59"/>
+      <c r="B81" s="67"/>
+      <c r="C81" s="67"/>
       <c r="D81" s="22"/>
       <c r="E81" s="3" t="s">
         <v>48</v>
@@ -22065,10 +24345,10 @@
       </c>
     </row>
     <row r="82" spans="2:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="59" t="s">
+      <c r="B82" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="C82" s="59">
+      <c r="C82" s="67">
         <v>12</v>
       </c>
       <c r="D82" s="30"/>
@@ -22160,8 +24440,8 @@
       </c>
     </row>
     <row r="83" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B83" s="59"/>
-      <c r="C83" s="59"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67"/>
       <c r="D83" s="22"/>
       <c r="E83" s="3" t="s">
         <v>48</v>
@@ -22251,10 +24531,10 @@
       </c>
     </row>
     <row r="84" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B84" s="59" t="s">
+      <c r="B84" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="C84" s="59">
+      <c r="C84" s="67">
         <v>13</v>
       </c>
       <c r="D84" s="22"/>
@@ -22298,8 +24578,8 @@
       </c>
     </row>
     <row r="85" spans="2:30" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="59"/>
-      <c r="C85" s="59"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="67"/>
       <c r="D85" s="25"/>
       <c r="E85" s="23" t="s">
         <v>48</v>
@@ -22389,10 +24669,10 @@
       </c>
     </row>
     <row r="86" spans="2:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="59" t="s">
+      <c r="B86" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="C86" s="59">
+      <c r="C86" s="67">
         <v>14</v>
       </c>
       <c r="D86" s="30"/>
@@ -22484,8 +24764,8 @@
       </c>
     </row>
     <row r="87" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B87" s="59"/>
-      <c r="C87" s="59"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67"/>
       <c r="D87" s="22"/>
       <c r="E87" s="3" t="s">
         <v>48</v>
@@ -22668,7 +24948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38195730-9354-4714-81F2-63A6F7EF56E7}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -22689,17 +24969,17 @@
     </row>
     <row r="2" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52"/>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62" t="s">
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70" t="s">
         <v>209</v>
       </c>
     </row>
@@ -22723,7 +25003,7 @@
       <c r="G3" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="H3" s="62"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="52" t="s">
@@ -22848,17 +25128,17 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="52"/>
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62" t="s">
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62" t="s">
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70" t="s">
         <v>209</v>
       </c>
     </row>
@@ -22882,7 +25162,7 @@
       <c r="G11" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="H11" s="62"/>
+      <c r="H11" s="70"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="52" t="s">
@@ -23022,6 +25302,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -23030,7 +25321,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F98E057C991C64EA8C44B2688F4F4E8" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="205ac32a36de600e2ab9bca4f1502e82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0278717-252d-455f-9297-341259384352" xmlns:ns3="67fd2e6b-9b4b-488b-ae5d-884371a2c380" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="423e538afa53ae88b73bb7a22e6ab62a" ns2:_="" ns3:_="">
     <xsd:import namespace="b0278717-252d-455f-9297-341259384352"/>
@@ -23219,18 +25510,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86E1DA6F-9828-4C90-B1DD-F6C5DDCFA33D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
+    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -23238,7 +25529,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32CEAB00-EB88-42CB-8573-B14217434AB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23255,15 +25546,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86E1DA6F-9828-4C90-B1DD-F6C5DDCFA33D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
-    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>